--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488035_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488035_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0038</v>
+        <v>5.7784</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6442</v>
+        <v>9.2783</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.6404</v>
+        <v>-3.5</v>
       </c>
       <c r="G2" t="n">
         <v>5.825</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3564</v>
+        <v>-0.5818</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8001</v>
+        <v>-0.166</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5562</v>
+        <v>-0.4158</v>
       </c>
       <c r="V2" t="n">
         <v>0.337</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1551</v>
+        <v>3.0803</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6545</v>
+        <v>1.4112</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5006</v>
+        <v>1.6691</v>
       </c>
       <c r="G3" t="n">
         <v>1.3474</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.094</v>
+        <v>0.0193</v>
       </c>
       <c r="T3" t="n">
-        <v>0.191</v>
+        <v>-0.0522</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0969</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0704</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. HUNT</t>
+          <t>S. MARTINEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1685</v>
+        <v>0.0543</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0754</v>
+        <v>2.3789</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9069</v>
+        <v>-2.3246</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1898</v>
+        <v>-1.1244</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2772</v>
+        <v>-1.379</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0874</v>
+        <v>0.2545</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7672</v>
+        <v>2.5436</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4062</v>
+        <v>0.1614</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.639</v>
+        <v>2.3822</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5775</v>
+        <v>-3.668</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.129</v>
+        <v>-1.5404</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4485</v>
+        <v>-2.1276</v>
       </c>
       <c r="P4" t="n">
         <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1805</v>
+        <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0609</v>
+        <v>-0.0789</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5688</v>
+        <v>-0.233</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5079</v>
+        <v>0.1541</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.9515</v>
+        <v>0.2666</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0663</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.0178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GUTIERREZ</t>
+          <t>B. HUNT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5488</v>
+        <v>0.0229</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1127</v>
+        <v>3.0983</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6615</v>
+        <v>-3.0754</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1244</v>
+        <v>1.1898</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.379</v>
+        <v>3.2772</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2545</v>
+        <v>-2.0874</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5436</v>
+        <v>3.7672</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1614</v>
+        <v>4.4062</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3822</v>
+        <v>-0.639</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.668</v>
+        <v>-2.5775</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5404</v>
+        <v>-1.129</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1276</v>
+        <v>-1.4485</v>
       </c>
       <c r="P5" t="n">
         <v>0.9911</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1893</v>
+        <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.2065</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4992</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1828</v>
+        <v>0.3394</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2666</v>
+        <v>-1.9515</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>1.0663</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.0178</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.111</v>
+        <v>-1.4842</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.9887</v>
+        <v>-3.3337</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8776</v>
+        <v>1.8496</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7582</v>
@@ -922,13 +922,13 @@
         <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8366</v>
+        <v>0.4634</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3047</v>
+        <v>-0.0403</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5037</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3053</v>
+        <v>-3.0465</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4757</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.781</v>
+        <v>-3.8091</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6631</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7631</v>
+        <v>0.022</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8077</v>
+        <v>0.0946</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0446</v>
+        <v>-0.0727</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8107</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9412</v>
+        <v>-3.1002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2455</v>
+        <v>0.0023</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1867</v>
+        <v>-3.1025</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6616</v>
@@ -1078,13 +1078,13 @@
         <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>0.203</v>
+        <v>0.044</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2423</v>
+        <v>-0.0009</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0393</v>
+        <v>0.0449</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0772</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6856</v>
+        <v>-3.1014</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2517</v>
+        <v>-2.5551</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.434</v>
+        <v>-0.5463</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0696</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8054</v>
+        <v>-0.2211</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0497</v>
+        <v>-0.3532</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2443</v>
+        <v>0.132</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>P. FERNANDEZ ANTUNEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5113</v>
+        <v>-4.3522</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1009</v>
+        <v>-2.3225</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4105</v>
+        <v>-2.0296</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9687</v>
+        <v>-4.3064</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1161</v>
+        <v>-0.6427</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8526</v>
+        <v>-3.6637</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7103</v>
+        <v>-0.9952</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6261</v>
+        <v>0.5523</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0842</v>
+        <v>-1.5475</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.6791</v>
+        <v>-3.3112</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7422</v>
+        <v>-1.195</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.9369</v>
+        <v>-2.1162</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7929</v>
+        <v>2.5769</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.18</v>
+        <v>-0.6028</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2577</v>
+        <v>-0.0883</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2666</v>
+        <v>-0.9405</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ ASTILLEROS</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9758</v>
+        <v>-4.3656</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.612</v>
+        <v>-0.1798</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3639</v>
+        <v>-4.1858</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2274</v>
+        <v>-3.9687</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2593</v>
+        <v>-1.1161</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.032</v>
+        <v>-2.8526</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1311</v>
+        <v>0.7103</v>
       </c>
       <c r="K11" t="n">
-        <v>3.0468</v>
+        <v>0.6261</v>
       </c>
       <c r="L11" t="n">
         <v>0.0842</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9037</v>
+        <v>-4.6791</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7875</v>
+        <v>-1.7422</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.1162</v>
+        <v>-2.9369</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.352</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.136</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4858</v>
+        <v>0.0679</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8736</v>
+        <v>0.101</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3594</v>
+        <v>-0.0331</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.337</v>
+        <v>-0.2666</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6036</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ ANTUNEZ</t>
+          <t>A. VAZQUEZ ASTILLEROS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0986</v>
+        <v>-5.4003</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9567</v>
+        <v>-4.3063</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1419</v>
+        <v>-1.0939</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3064</v>
+        <v>0.2274</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6427</v>
+        <v>2.2593</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.6637</v>
+        <v>-2.032</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9952</v>
+        <v>3.1311</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5523</v>
+        <v>3.0468</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5475</v>
+        <v>0.0842</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.3112</v>
+        <v>-2.9037</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.195</v>
+        <v>-0.7875</v>
       </c>
       <c r="O12" t="n">
         <v>-2.1162</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5858</v>
+        <v>-5.352</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9911</v>
+        <v>-7.136</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5769</v>
+        <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4375</v>
+        <v>0.0614</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2369</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2006</v>
+        <v>0.6293</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9405</v>
+        <v>-0.337</v>
       </c>
       <c r="W12" t="n">
         <v>0.2666</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2071</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.8502</v>
+        <v>-15.9145</v>
       </c>
       <c r="E13" t="n">
-        <v>3.298000000000001</v>
+        <v>4.2342</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.1486</v>
+        <v>-20.1485</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.962400000000001</v>
+        <v>-7.9624</v>
       </c>
       <c r="H13" t="n">
         <v>8.051399999999999</v>
@@ -1459,7 +1459,7 @@
         <v>-17.8804</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.8399</v>
@@ -1468,13 +1468,13 @@
         <v>17.8402</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.037500000000001</v>
+        <v>-1.1013</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3026</v>
+        <v>-2.3667</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2653</v>
+        <v>1.265</v>
       </c>
       <c r="V13" t="n">
         <v>-6.850300000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8185</v>
+        <v>4.8465</v>
       </c>
       <c r="E14" t="n">
         <v>5.6786</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8602</v>
+        <v>-0.8321</v>
       </c>
       <c r="G14" t="n">
         <v>1.9195</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>0.228</v>
+        <v>0.2561</v>
       </c>
       <c r="T14" t="n">
         <v>-0.132</v>
       </c>
       <c r="U14" t="n">
-        <v>0.36</v>
+        <v>0.3881</v>
       </c>
       <c r="V14" t="n">
         <v>1.8781</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7729</v>
+        <v>4.42</v>
       </c>
       <c r="E15" t="n">
-        <v>4.464</v>
+        <v>4.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3089</v>
+        <v>-0.38</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7092</v>
+        <v>0.2451</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1894</v>
+        <v>-2.3529</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5198</v>
+        <v>2.5981</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8211</v>
+        <v>2.9673</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3185</v>
+        <v>0.1147</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5027</v>
+        <v>2.8526</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1119</v>
+        <v>-2.7222</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.129</v>
+        <v>-2.4676</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0171</v>
+        <v>-0.2545</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1805</v>
+        <v>-1.1893</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6504</v>
+        <v>0.4267</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1944</v>
+        <v>-0.2623</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8448</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6115</v>
+        <v>3.3517</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0178</v>
+        <v>3.2843</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4063</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.61</v>
+        <v>4.1995</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7169</v>
+        <v>4.2603</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1069</v>
+        <v>-0.0607</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8234</v>
+        <v>2.7092</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0458</v>
+        <v>0.1894</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8692</v>
+        <v>2.5198</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8811</v>
+        <v>3.8211</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3499</v>
+        <v>1.3185</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5312</v>
+        <v>2.5027</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0577</v>
+        <v>-1.1119</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3957</v>
+        <v>-1.129</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.662</v>
+        <v>0.0171</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9342</v>
+        <v>0.077</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1638</v>
+        <v>-0.3982</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7704</v>
+        <v>0.4752</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.337</v>
+        <v>1.6115</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8701</v>
+        <v>3.0178</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2071</v>
+        <v>-1.4063</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7572</v>
+        <v>3.2824</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1888</v>
+        <v>3.6982</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4316</v>
+        <v>-0.4158</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2451</v>
+        <v>1.8234</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3529</v>
+        <v>-0.0458</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5981</v>
+        <v>1.8692</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9673</v>
+        <v>2.8811</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1147</v>
+        <v>0.3499</v>
       </c>
       <c r="L17" t="n">
-        <v>2.8526</v>
+        <v>2.5312</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7222</v>
+        <v>-1.0577</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.4676</v>
+        <v>-0.3957</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2545</v>
+        <v>-0.662</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2361</v>
+        <v>0.6066</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8736</v>
+        <v>0.1451</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6375</v>
+        <v>0.4615</v>
       </c>
       <c r="V17" t="n">
-        <v>3.3517</v>
+        <v>-0.337</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2843</v>
+        <v>0.8701</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0674</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.33</v>
+        <v>2.8394</v>
       </c>
       <c r="E18" t="n">
-        <v>1.917</v>
+        <v>2.4264</v>
       </c>
       <c r="F18" t="n">
         <v>0.413</v>
@@ -1858,10 +1858,10 @@
         <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.334</v>
+        <v>0.1753</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4992</v>
+        <v>0.0102</v>
       </c>
       <c r="U18" t="n">
         <v>0.1651</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1991</v>
+        <v>2.8162</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8179</v>
+        <v>2.3273</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3812</v>
+        <v>0.489</v>
       </c>
       <c r="G19" t="n">
         <v>2.0366</v>
@@ -1936,13 +1936,13 @@
         <v>2.3787</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7602</v>
+        <v>-0.1432</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7488</v>
+        <v>-0.2394</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0115</v>
+        <v>0.0963</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2666</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1107</v>
+        <v>2.4884</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1107</v>
+        <v>2.6289</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.1406</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1107</v>
+        <v>-0.4714</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3027</v>
+        <v>-1.0989</v>
       </c>
       <c r="I20" t="n">
-        <v>1.808</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1107</v>
+        <v>1.8569</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3027</v>
+        <v>1.6482</v>
       </c>
       <c r="L20" t="n">
-        <v>1.808</v>
+        <v>0.2087</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-2.3283</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-2.7471</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.4189</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.3056</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.4037</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5506</v>
+        <v>2.1107</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9158</v>
+        <v>2.1107</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3652</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4714</v>
+        <v>2.1107</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0989</v>
+        <v>0.3027</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6274999999999999</v>
+        <v>1.808</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8569</v>
+        <v>2.1107</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6482</v>
+        <v>0.3027</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2087</v>
+        <v>1.808</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3283</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.7471</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4189</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6321</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8112</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1791</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6171</v>
+        <v>-1.193</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6314</v>
+        <v>-2.0389</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0144</v>
+        <v>0.8459</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6112</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1725</v>
+        <v>0.5966</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4847</v>
+        <v>0.0772</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6878</v>
+        <v>0.5193</v>
       </c>
       <c r="V23" t="n">
         <v>0.4074</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-1.2026</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0361</v>
+        <v>-0.6474</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8595</v>
+        <v>-0.5552</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1789</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7401</v>
+        <v>0.4332</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7967</v>
+        <v>0.1855</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0566</v>
+        <v>0.2477</v>
       </c>
       <c r="V24" t="n">
         <v>0.1378</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8007</v>
+        <v>-2.2646</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7283</v>
+        <v>-1.5246</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0724</v>
+        <v>-0.74</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7453</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5995</v>
+        <v>-0.0633</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2496</v>
+        <v>-0.0459</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3499</v>
+        <v>-0.0175</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2666</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9423</v>
+        <v>-2.6158</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6138</v>
+        <v>-1.5119</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3285</v>
+        <v>-1.1039</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8989</v>
@@ -2482,13 +2482,13 @@
         <v>0.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5697</v>
+        <v>-0.2432</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1329</v>
+        <v>0.0917</v>
       </c>
       <c r="V26" t="n">
         <v>-0.8701</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.551</v>
+        <v>-3.7057</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.1595</v>
+        <v>-3.567</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3914</v>
+        <v>-0.1387</v>
       </c>
       <c r="G27" t="n">
         <v>-2.8729</v>
@@ -2560,13 +2560,13 @@
         <v>1.1893</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4439</v>
+        <v>0.2891</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2351</v>
+        <v>-0.1724</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2088</v>
+        <v>0.4615</v>
       </c>
       <c r="V27" t="n">
         <v>0.0674</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>16.8502</v>
+        <v>17.5294</v>
       </c>
       <c r="E28" t="n">
         <v>20.14859999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.2982</v>
+        <v>-2.6191</v>
       </c>
       <c r="G28" t="n">
         <v>7.9625</v>
@@ -2611,7 +2611,7 @@
         <v>16.0141</v>
       </c>
       <c r="J28" t="n">
-        <v>28.5306</v>
+        <v>28.53059999999999</v>
       </c>
       <c r="K28" t="n">
         <v>10.6504</v>
@@ -2638,16 +2638,16 @@
         <v>17.8401</v>
       </c>
       <c r="S28" t="n">
-        <v>2.0375</v>
+        <v>2.7165</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.2653</v>
+        <v>-1.2652</v>
       </c>
       <c r="U28" t="n">
-        <v>3.302600000000001</v>
+        <v>3.981599999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>6.850300000000001</v>
+        <v>6.8503</v>
       </c>
       <c r="W28" t="n">
         <v>10.7231</v>
